--- a/backend/data/data_all.xlsx
+++ b/backend/data/data_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alan\Github Projects\roco-kingdom-team-builder\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8E3E83-D710-4ABA-A20C-C204E513BED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD086E43-F539-4878-8B28-B621B1042097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="技能表" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
